--- a/data/dividends_info_20260704.xlsx
+++ b/data/dividends_info_20260704.xlsx
@@ -4356,7 +4356,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4373,7 +4373,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -4526,7 +4526,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4543,7 +4543,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4560,7 +4560,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4577,7 +4577,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4587,14 +4587,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4604,14 +4604,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4628,7 +4628,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4638,14 +4638,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4655,14 +4655,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4672,14 +4672,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4696,7 +4696,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4706,14 +4706,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4723,14 +4723,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4747,7 +4747,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4764,7 +4764,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4774,14 +4774,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4791,14 +4791,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4815,7 +4815,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4849,7 +4849,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4859,14 +4859,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4876,14 +4876,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4893,14 +4893,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4910,14 +4910,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4927,14 +4927,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4951,7 +4951,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4961,14 +4961,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4985,7 +4985,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -5002,7 +5002,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5012,14 +5012,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5036,7 +5036,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5046,14 +5046,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5070,7 +5070,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5080,14 +5080,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>CASTELLO SGR S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5097,14 +5097,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5114,14 +5114,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5131,14 +5131,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5155,7 +5155,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5165,14 +5165,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5182,14 +5182,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5206,7 +5206,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5216,14 +5216,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5240,7 +5240,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5250,14 +5250,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5267,14 +5267,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5284,14 +5284,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5308,7 +5308,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>CASTELLO SGR S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5325,7 +5325,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5335,14 +5335,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5352,14 +5352,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5376,7 +5376,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5393,7 +5393,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5403,14 +5403,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5427,7 +5427,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5444,7 +5444,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5454,14 +5454,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5471,14 +5471,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5488,14 +5488,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5512,7 +5512,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5529,7 +5529,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -5539,14 +5539,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -5556,14 +5556,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -5573,14 +5573,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -5631,7 +5631,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -5641,14 +5641,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -5658,14 +5658,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -5675,14 +5675,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -5692,14 +5692,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -5709,14 +5709,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -5726,14 +5726,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -5743,14 +5743,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -5760,14 +5760,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -5777,14 +5777,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -5794,14 +5794,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -5811,14 +5811,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -5828,14 +5828,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
@@ -5862,14 +5862,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5879,14 +5879,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5896,14 +5896,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5920,7 +5920,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5937,7 +5937,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5947,14 +5947,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5964,14 +5964,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -6005,7 +6005,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -6043,146 +6043,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Alfonsino S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Anima Holding S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CLABO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ENAV S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>EuroGroup Laminations S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>